--- a/ECMAC.xlsx
+++ b/ECMAC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="52">
   <si>
     <t/>
   </si>
@@ -130,37 +130,34 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
+    <t>20120400</t>
+  </si>
+  <si>
+    <t>SONY GIFT CARD 100K</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>20124879</t>
   </si>
   <si>
     <t>NTFLX GIFT CARD 160K</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>20133887</t>
   </si>
   <si>
     <t>SMRTFN SP LONGLF 90D</t>
   </si>
   <si>
-    <t>20120400</t>
-  </si>
-  <si>
-    <t>SONY GIFT CARD 100K</t>
+    <t>20081617</t>
+  </si>
+  <si>
+    <t>XL PERDANA XTRA FUN</t>
   </si>
   <si>
     <t>10</t>
-  </si>
-  <si>
-    <t>20081617</t>
-  </si>
-  <si>
-    <t>XL PERDANA XTRA FUN</t>
-  </si>
-  <si>
-    <t>11</t>
   </si>
   <si>
     <t>RT,(E-2)</t>
@@ -890,7 +887,7 @@
         <v>41</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -907,39 +904,39 @@
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
@@ -947,7 +944,7 @@
         <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>38</v>
